--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -13,484 +13,6 @@
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Dillon Walton</author>
-  </authors>
-  <commentList>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{C5AC19FE-CD97-4247-B105-54CE2CCB2A22}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dillon Walton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>q226 v3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{62359BE1-BB6F-BA4C-94EF-44C9612A9B81}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dillon Walton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>q226 v3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{09414612-5B8E-F54E-B869-B183750B0F35}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dillon Walton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>q226 v3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{63810956-4E6C-5744-A6FF-680D417501F9}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dillon Walton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>powerwall 3p = three phase</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={38726785-892C-804C-8FF8-DADB51549DC9}</author>
-    <author>tc={925AD150-B139-6741-9EC2-6FE911D37EFF}</author>
-    <author>tc={00827756-8C87-FC4E-BC39-F490C56C50B7}</author>
-    <author>tc={6BB9B9F4-FBF5-9B49-8159-98C3A5C6D3BD}</author>
-    <author>tc={978DD6E5-58E1-9F42-A7E1-A314658D4B6C}</author>
-    <author>tc={9F91B916-055A-A946-9CCD-A1E2DB92D76A}</author>
-    <author>tc={A822EA57-979C-C248-99FD-6E63FC7EFEDC}</author>
-    <author>tc={DA7FB16A-BE59-1C4E-AEE1-B3F29AEC4585}</author>
-    <author>tc={28B12050-6E57-1549-88E4-6182ECE76F21}</author>
-    <author>tc={E50E5CDA-5BF9-BA4A-B00E-EE3CD7609C8F}</author>
-    <author>tc={4ACDDBCB-916E-7242-9A04-C86391B224F5}</author>
-    <author>tc={82B56D2A-B009-2049-A96C-28DAEAF35590}</author>
-    <author>tc={1D287C6F-E2D2-E345-BE86-5BE0D8B9902E}</author>
-    <author>tc={35C48961-CBB3-054F-AB67-BC31DA5D496E}</author>
-    <author>tc={2B43781E-258D-B846-ADF9-31DF09F42242}</author>
-    <author>tc={D67A7C5D-6506-2244-878D-DB7D6AF3E3A5}</author>
-    <author>tc={762FEB78-F3D7-6C42-9A3A-8D6E51523308}</author>
-    <author>tc={F1607007-8EEC-9642-B09C-96725A8DDB3D}</author>
-    <author>tc={68BF9E4D-74F3-1E45-AB40-9313600989E6}</author>
-    <author>tc={AB337D9C-E292-2143-B82D-380CAA0E7A81}</author>
-    <author>tc={77FB4DF4-DAF2-6E44-9ADD-0BFD928990F8}</author>
-    <author>tc={FC305755-3C2E-6748-88FA-76EFEFFEC1DA}</author>
-    <author>tc={58D8461D-D8C7-F644-A557-CB2165FF1C7B}</author>
-    <author>tc={F9526E8C-ABD1-B444-95D9-E6D2FD4DA32E}</author>
-    <author>tc={B4213311-BB2C-BC4D-A1BC-81FAD250A680}</author>
-    <author>tc={C4663125-B0BD-7E48-8EE8-B212C568F57F}</author>
-    <author>Dillon Walton</author>
-  </authors>
-  <commentList>
-    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{38726785-892C-804C-8FF8-DADB51549DC9}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q120 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA_Update_Letter_2020-1Q</t>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="1" shapeId="0" xr:uid="{925AD150-B139-6741-9EC2-6FE911D37EFF}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q220 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA_Update_Letter_2020-2Q</t>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="2" shapeId="0" xr:uid="{00827756-8C87-FC4E-BC39-F490C56C50B7}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q320 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2020-Update</t>
-      </text>
-    </comment>
-    <comment ref="F2" authorId="3" shapeId="0" xr:uid="{6BB9B9F4-FBF5-9B49-8159-98C3A5C6D3BD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q420 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2020-Update</t>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="4" shapeId="0" xr:uid="{978DD6E5-58E1-9F42-A7E1-A314658D4B6C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q121 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2021-Update</t>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="5" shapeId="0" xr:uid="{9F91B916-055A-A946-9CCD-A1E2DB92D76A}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q221 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2021-Update</t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="6" shapeId="0" xr:uid="{A822EA57-979C-C248-99FD-6E63FC7EFEDC}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q321 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2021-Quarterly-Update</t>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="7" shapeId="0" xr:uid="{DA7FB16A-BE59-1C4E-AEE1-B3F29AEC4585}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q421 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2021-Update</t>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="8" shapeId="0" xr:uid="{28B12050-6E57-1549-88E4-6182ECE76F21}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q122 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2022-Update</t>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="9" shapeId="0" xr:uid="{E50E5CDA-5BF9-BA4A-B00E-EE3CD7609C8F}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q222 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2022-Update</t>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="10" shapeId="0" xr:uid="{4ACDDBCB-916E-7242-9A04-C86391B224F5}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q322 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2022-Update</t>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="11" shapeId="0" xr:uid="{82B56D2A-B009-2049-A96C-28DAEAF35590}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q422 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2022-Update</t>
-      </text>
-    </comment>
-    <comment ref="O2" authorId="12" shapeId="0" xr:uid="{1D287C6F-E2D2-E345-BE86-5BE0D8B9902E}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q123 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2023-Update</t>
-      </text>
-    </comment>
-    <comment ref="P2" authorId="13" shapeId="0" xr:uid="{35C48961-CBB3-054F-AB67-BC31DA5D496E}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q223 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2023-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="Q2" authorId="14" shapeId="0" xr:uid="{2B43781E-258D-B846-ADF9-31DF09F42242}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q323 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2023-Update-3.pdf</t>
-      </text>
-    </comment>
-    <comment ref="R2" authorId="15" shapeId="0" xr:uid="{D67A7C5D-6506-2244-878D-DB7D6AF3E3A5}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q423 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2023-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="S2" authorId="16" shapeId="0" xr:uid="{762FEB78-F3D7-6C42-9A3A-8D6E51523308}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q124 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2024-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="T2" authorId="17" shapeId="0" xr:uid="{F1607007-8EEC-9642-B09C-96725A8DDB3D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q224 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2024-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="U2" authorId="18" shapeId="0" xr:uid="{68BF9E4D-74F3-1E45-AB40-9313600989E6}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q324 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2024-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="V2" authorId="19" shapeId="0" xr:uid="{AB337D9C-E292-2143-B82D-380CAA0E7A81}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q424 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2024-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="W2" authorId="20" shapeId="0" xr:uid="{77FB4DF4-DAF2-6E44-9ADD-0BFD928990F8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q125 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/IR/TSLA-Q1-2025-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="X2" authorId="21" shapeId="0" xr:uid="{FC305755-3C2E-6748-88FA-76EFEFFEC1DA}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q225 Tesla shareholder letter
-https://www.tesla.com/sites/default/files/downloads/TSLA-Q2-2025-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="Y2" authorId="22" shapeId="0" xr:uid="{58D8461D-D8C7-F644-A557-CB2165FF1C7B}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q325 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q3-2025-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="Z2" authorId="23" shapeId="0" xr:uid="{F9526E8C-ABD1-B444-95D9-E6D2FD4DA32E}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q425 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q4-2025-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="AA2" authorId="24" shapeId="0" xr:uid="{B4213311-BB2C-BC4D-A1BC-81FAD250A680}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q126 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q1-2026-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="AB2" authorId="25" shapeId="0" xr:uid="{C4663125-B0BD-7E48-8EE8-B212C568F57F}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Q226 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q2-2026-Update.pdf</t>
-      </text>
-    </comment>
-    <comment ref="B72" authorId="26" shapeId="0" xr:uid="{AC8DE0E4-639A-984D-AC99-F9922FE5CB6D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dillon Walton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Book value lease assets</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B73" authorId="26" shapeId="0" xr:uid="{D6126DBB-7434-9D4F-B554-4C63A31DF33F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dillon Walton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Book value of leased assets</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1370,115 +892,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C2" dT="2026-08-29T01:38:23.16" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{38726785-892C-804C-8FF8-DADB51549DC9}">
-    <text>Q120 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA_Update_Letter_2020-1Q</text>
-  </threadedComment>
-  <threadedComment ref="D2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{925AD150-B139-6741-9EC2-6FE911D37EFF}">
-    <text>Q220 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA_Update_Letter_2020-2Q</text>
-  </threadedComment>
-  <threadedComment ref="E2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{00827756-8C87-FC4E-BC39-F490C56C50B7}">
-    <text>Q320 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2020-Update</text>
-  </threadedComment>
-  <threadedComment ref="F2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{6BB9B9F4-FBF5-9B49-8159-98C3A5C6D3BD}">
-    <text>Q420 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2020-Update</text>
-  </threadedComment>
-  <threadedComment ref="G2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{978DD6E5-58E1-9F42-A7E1-A314658D4B6C}">
-    <text>Q121 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2021-Update</text>
-  </threadedComment>
-  <threadedComment ref="H2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{9F91B916-055A-A946-9CCD-A1E2DB92D76A}">
-    <text>Q221 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2021-Update</text>
-  </threadedComment>
-  <threadedComment ref="I2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{A822EA57-979C-C248-99FD-6E63FC7EFEDC}">
-    <text>Q321 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2021-Quarterly-Update</text>
-  </threadedComment>
-  <threadedComment ref="J2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{DA7FB16A-BE59-1C4E-AEE1-B3F29AEC4585}">
-    <text>Q421 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2021-Update</text>
-  </threadedComment>
-  <threadedComment ref="K2" dT="2026-08-29T01:38:23.18" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{28B12050-6E57-1549-88E4-6182ECE76F21}">
-    <text>Q122 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2022-Update</text>
-  </threadedComment>
-  <threadedComment ref="L2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{E50E5CDA-5BF9-BA4A-B00E-EE3CD7609C8F}">
-    <text>Q222 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2022-Update</text>
-  </threadedComment>
-  <threadedComment ref="M2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{4ACDDBCB-916E-7242-9A04-C86391B224F5}">
-    <text>Q322 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2022-Update</text>
-  </threadedComment>
-  <threadedComment ref="N2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{82B56D2A-B009-2049-A96C-28DAEAF35590}">
-    <text>Q422 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2022-Update</text>
-  </threadedComment>
-  <threadedComment ref="O2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{1D287C6F-E2D2-E345-BE86-5BE0D8B9902E}">
-    <text>Q123 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2023-Update</text>
-  </threadedComment>
-  <threadedComment ref="P2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{35C48961-CBB3-054F-AB67-BC31DA5D496E}">
-    <text>Q223 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2023-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="Q2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{2B43781E-258D-B846-ADF9-31DF09F42242}">
-    <text>Q323 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2023-Update-3.pdf</text>
-  </threadedComment>
-  <threadedComment ref="R2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{D67A7C5D-6506-2244-878D-DB7D6AF3E3A5}">
-    <text>Q423 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2023-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="S2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{762FEB78-F3D7-6C42-9A3A-8D6E51523308}">
-    <text>Q124 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q1-2024-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="T2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{F1607007-8EEC-9642-B09C-96725A8DDB3D}">
-    <text>Q224 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q2-2024-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="U2" dT="2026-08-29T01:38:23.19" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{68BF9E4D-74F3-1E45-AB40-9313600989E6}">
-    <text>Q324 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q3-2024-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="V2" dT="2026-08-29T01:38:23.20" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{AB337D9C-E292-2143-B82D-380CAA0E7A81}">
-    <text>Q424 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/TSLA-Q4-2024-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="W2" dT="2026-08-29T01:38:23.20" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{77FB4DF4-DAF2-6E44-9ADD-0BFD928990F8}">
-    <text>Q125 Tesla shareholder letter
-https://digitalassets.tesla.com/tesla-contents/image/upload/IR/IR/TSLA-Q1-2025-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="X2" dT="2026-08-29T01:38:23.20" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{FC305755-3C2E-6748-88FA-76EFEFFEC1DA}">
-    <text>Q225 Tesla shareholder letter
-https://www.tesla.com/sites/default/files/downloads/TSLA-Q2-2025-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="Y2" dT="2026-08-29T01:38:23.20" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{58D8461D-D8C7-F644-A557-CB2165FF1C7B}">
-    <text>Q325 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q3-2025-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="Z2" dT="2026-08-29T01:38:23.20" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{F9526E8C-ABD1-B444-95D9-E6D2FD4DA32E}">
-    <text>Q425 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q4-2025-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="AA2" dT="2026-08-29T01:38:23.20" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{B4213311-BB2C-BC4D-A1BC-81FAD250A680}">
-    <text>Q126 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q1-2026-Update.pdf</text>
-  </threadedComment>
-  <threadedComment ref="AB2" dT="2026-08-29T01:38:23.21" personId="{72341B3D-64ED-DE40-92E1-1286D6A616CD}" id="{C4663125-B0BD-7E48-8EE8-B212C568F57F}">
-    <text>Q226 Tesla shareholder letter
-https://assets-ir.tesla.com/tesla-contents/IR/TSLA-Q2-2026-Update.pdf</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -82,6 +82,13 @@
       <sz val="12"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <i val="1"/>
+      <color rgb="FF7030A0"/>
+      <sz val="12"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -104,7 +111,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,6 +127,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1307,7 +1315,7 @@
           <t>Q421</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>Q122</t>
         </is>
@@ -1337,22 +1345,22 @@
           <t>Q223</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="13" t="inlineStr">
         <is>
           <t>Q323</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>Q423</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="13" t="inlineStr">
         <is>
           <t>Q124</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="T2" s="13" t="inlineStr">
         <is>
           <t>Q224</t>
         </is>
@@ -3466,7 +3474,6 @@
     <row r="96">
       <c r="Z96" s="1" t="n"/>
     </row>
-    <row r="97"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -3477,22 +3484,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T2" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA2" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
 </worksheet>
 </file>
--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB5873B-7106-4F08-B51E-2DCB378B8401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5933EB-5B7F-46C5-AD58-977DDA7B96F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{969D4ED5-6A32-DE48-841A-E0A03F4B02B5}"/>
   </bookViews>
@@ -1948,14 +1948,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BB641C-A60E-1D48-998E-8C4C1E1253D6}">
-  <dimension ref="A2:CG96"/>
+  <dimension ref="A2:CU96"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
     <col min="3" max="41" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:99" x14ac:dyDescent="0.25">
       <c r="C2" s="13" t="s">
         <v>138</v>
       </c>
@@ -2182,28 +2182,70 @@
         <v>36</v>
       </c>
       <c r="CA2">
+        <v>2010</v>
+      </c>
+      <c r="CB2">
+        <v>2011</v>
+      </c>
+      <c r="CC2">
+        <v>2012</v>
+      </c>
+      <c r="CD2">
+        <v>2013</v>
+      </c>
+      <c r="CE2">
+        <v>2014</v>
+      </c>
+      <c r="CF2">
+        <v>2015</v>
+      </c>
+      <c r="CG2">
+        <v>2016</v>
+      </c>
+      <c r="CH2">
+        <v>2017</v>
+      </c>
+      <c r="CI2">
+        <v>2018</v>
+      </c>
+      <c r="CJ2">
+        <v>2019</v>
+      </c>
+      <c r="CK2">
+        <v>2020</v>
+      </c>
+      <c r="CL2">
+        <v>2021</v>
+      </c>
+      <c r="CM2">
+        <v>2022</v>
+      </c>
+      <c r="CN2">
+        <v>2023</v>
+      </c>
+      <c r="CO2">
         <v>2024</v>
       </c>
-      <c r="CB2">
+      <c r="CP2">
         <v>2025</v>
       </c>
-      <c r="CC2">
+      <c r="CQ2">
         <v>2026</v>
       </c>
-      <c r="CD2">
+      <c r="CR2">
         <v>2027</v>
       </c>
-      <c r="CE2">
+      <c r="CS2">
         <v>2028</v>
       </c>
-      <c r="CF2">
+      <c r="CT2">
         <v>2029</v>
       </c>
-      <c r="CG2">
+      <c r="CU2">
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:99" x14ac:dyDescent="0.25">
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
       <c r="AR3" s="2"/>
@@ -2231,7 +2273,7 @@
       <c r="BN3" s="2"/>
       <c r="BO3" s="2"/>
     </row>
-    <row r="4" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -2265,7 +2307,7 @@
       <c r="BN4" s="2"/>
       <c r="BO4" s="2"/>
     </row>
-    <row r="5" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:99" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>105</v>
       </c>
@@ -2296,7 +2338,7 @@
       <c r="BN5" s="2"/>
       <c r="BO5" s="2"/>
     </row>
-    <row r="6" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:99" x14ac:dyDescent="0.25">
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2"/>
       <c r="AR6" s="2"/>
@@ -2324,7 +2366,7 @@
       <c r="BN6" s="2"/>
       <c r="BO6" s="2"/>
     </row>
-    <row r="7" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:99" x14ac:dyDescent="0.25">
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2"/>
       <c r="AR7" s="2"/>
@@ -2352,7 +2394,7 @@
       <c r="BN7" s="2"/>
       <c r="BO7" s="2"/>
     </row>
-    <row r="8" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:99" x14ac:dyDescent="0.25">
       <c r="AP8" s="2"/>
       <c r="AQ8" s="2"/>
       <c r="AR8" s="2"/>
@@ -2380,7 +2422,7 @@
       <c r="BN8" s="2"/>
       <c r="BO8" s="2"/>
     </row>
-    <row r="9" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:99" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -2448,7 +2490,7 @@
       <c r="BN9" s="2"/>
       <c r="BO9" s="2"/>
     </row>
-    <row r="10" spans="1:85" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:99" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>93</v>
       </c>
@@ -2487,7 +2529,7 @@
       <c r="BT10" s="11"/>
       <c r="BU10" s="11"/>
     </row>
-    <row r="11" spans="1:85" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:99" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>94</v>
       </c>
@@ -2526,7 +2568,7 @@
       <c r="BT11" s="11"/>
       <c r="BU11" s="11"/>
     </row>
-    <row r="12" spans="1:85" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:99" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>95</v>
       </c>
@@ -2563,7 +2605,7 @@
       <c r="BQ12" s="1"/>
       <c r="BR12" s="1"/>
     </row>
-    <row r="13" spans="1:85" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:99" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AP13" s="9"/>
       <c r="AQ13" s="9"/>
       <c r="AR13" s="9"/>
@@ -2594,7 +2636,7 @@
       <c r="BQ13" s="1"/>
       <c r="BR13" s="1"/>
     </row>
-    <row r="14" spans="1:85" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:99" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
         <v>96</v>
       </c>
@@ -2628,7 +2670,7 @@
       <c r="BQ14" s="1"/>
       <c r="BR14" s="1"/>
     </row>
-    <row r="15" spans="1:85" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:99" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>97</v>
       </c>
@@ -2662,7 +2704,7 @@
       <c r="BQ15" s="1"/>
       <c r="BR15" s="1"/>
     </row>
-    <row r="16" spans="1:85" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:99" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AP16" s="9"/>
       <c r="AQ16" s="9"/>
       <c r="AR16" s="9"/>

--- a/TSLA.xlsx
+++ b/TSLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5933EB-5B7F-46C5-AD58-977DDA7B96F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8240D41D-D31A-4D07-94CF-69BC3D7A3A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{969D4ED5-6A32-DE48-841A-E0A03F4B02B5}"/>
   </bookViews>
@@ -519,7 +519,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="179">
   <si>
     <t>Revenue</t>
   </si>
@@ -1050,6 +1050,12 @@
   </si>
   <si>
     <t>Q419</t>
+  </si>
+  <si>
+    <t>10-Q</t>
+  </si>
+  <si>
+    <t>10-K</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1065,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1140,6 +1146,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1163,7 +1177,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1179,6 +1193,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1203,32 +1218,77 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>67</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>25400</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>67</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75585CDC-7B72-4EE2-6630-4B94E900971F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23152100" y="88900"/>
-          <a:ext cx="0" cy="7480300"/>
-        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>94</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>94</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
@@ -1948,13 +2008,210 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BB641C-A60E-1D48-998E-8C4C1E1253D6}">
-  <dimension ref="A2:CU96"/>
+  <dimension ref="A1:CU96"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
     <col min="3" max="41" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="C1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AH1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AL1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AP1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AT1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AU1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AV1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AW1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AX1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AY1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BA1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="BB1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BC1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BD1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BE1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="BF1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BG1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BH1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="BJ1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BK1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BL1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BM1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="BN1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="BO1" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
     <row r="2" spans="1:99" x14ac:dyDescent="0.25">
       <c r="C2" s="13" t="s">
         <v>138</v>
@@ -4300,9 +4557,74 @@
     <hyperlink ref="BM2" r:id="rId63" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828026000016/exhibit9914.htm" xr:uid="{D5460E44-574E-4573-85D3-592DE209CB2E}"/>
     <hyperlink ref="BN2" r:id="rId64" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828026022956/exhibit9911111.htm" xr:uid="{867EC697-FD99-427F-AD6E-A26B7C2EB105}"/>
     <hyperlink ref="BO2" r:id="rId65" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828026046717/exhibit99111111.htm" xr:uid="{7EB23F8D-E5FF-4BB9-A1F2-DD9AAEBBE8CF}"/>
+    <hyperlink ref="C1" r:id="rId66" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312510188792/d10q.htm" xr:uid="{C37FF7F6-DC06-4BF4-8339-D16C945BE566}"/>
+    <hyperlink ref="D1" r:id="rId67" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312510259068/d10q.htm" xr:uid="{D6BA29A2-86B2-42FA-86ED-6AC8568032CA}"/>
+    <hyperlink ref="E1" r:id="rId68" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312511054847/d10k.htm" xr:uid="{D9F3EB19-29E6-4BA8-9734-F286AF488390}"/>
+    <hyperlink ref="F1" r:id="rId69" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312511139677/d10q.htm" xr:uid="{1065D40C-C974-4E0A-B79C-BEA4DD1E0F68}"/>
+    <hyperlink ref="G1" r:id="rId70" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312511221497/d10q.htm" xr:uid="{6748B4EB-B470-4429-BC4D-4A04C3889BB0}"/>
+    <hyperlink ref="H1" r:id="rId71" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312511308489/d226201d10q.htm" xr:uid="{31C76DA4-7ABF-4C0A-9648-B3260BFF3BEA}"/>
+    <hyperlink ref="I1" r:id="rId72" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312512081990/d279413d10k.htm" xr:uid="{A27A25C2-82F8-464E-AB8B-C376F659A41E}"/>
+    <hyperlink ref="J1" r:id="rId73" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312512225825/d325967d10q.htm" xr:uid="{043D89D5-5DE0-4A3C-83B8-73745E07F96A}"/>
+    <hyperlink ref="K1" r:id="rId74" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312512332138/d364775d10q.htm" xr:uid="{B77CAC36-0CF5-4A77-A2BF-DB3FF4D07824}"/>
+    <hyperlink ref="L1" r:id="rId75" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312512457610/d410318d10q.htm" xr:uid="{7E527949-E26D-47CA-A8BC-CEFE42D1F1A0}"/>
+    <hyperlink ref="M1" r:id="rId76" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312513096241/d452995d10k.htm" xr:uid="{3CACE7CF-38F1-495F-80D3-EAFBA275E945}"/>
+    <hyperlink ref="N1" r:id="rId77" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312513212354/d511008d10q.htm" xr:uid="{DE1732E9-2E08-44B0-AD1D-366236D37C1F}"/>
+    <hyperlink ref="O1" r:id="rId78" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312513327916/d549636d10q.htm" xr:uid="{B201FF2C-9AC9-43FB-A64E-CAC809EBEE40}"/>
+    <hyperlink ref="P1" r:id="rId79" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312513435480/d588506d10q.htm" xr:uid="{998FD970-4FC3-4F10-BFC4-EEC65B75FCE6}"/>
+    <hyperlink ref="Q1" r:id="rId80" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312514069681/d668062d10k.htm" xr:uid="{C2468465-647D-4C2E-9AEA-0FAF5D9183B7}"/>
+    <hyperlink ref="R1" r:id="rId81" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312514192606/d715897d10q.htm" xr:uid="{053B05AB-0060-4955-BB40-58ED0EFFCE53}"/>
+    <hyperlink ref="S1" r:id="rId82" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312514303175/d766922d10q.htm" xr:uid="{EADD4861-A298-4ADB-AF81-93A81D95FDFC}"/>
+    <hyperlink ref="T1" r:id="rId83" display="https://www.sec.gov/Archives/edgar/data/1318605/000119312514403635/d812482d10q.htm" xr:uid="{6F56251F-F778-4CE2-9E68-4A02FC584708}"/>
+    <hyperlink ref="U1" r:id="rId84" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459015001031/tsla-10k_20141231.htm" xr:uid="{C7D8C8EA-A1A3-4C81-8EC7-194B897A510F}"/>
+    <hyperlink ref="V1" r:id="rId85" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459015003789/tsla-10q_20150331.htm" xr:uid="{AF91A03E-F810-401F-BECB-0DAA561A138C}"/>
+    <hyperlink ref="W1" r:id="rId86" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459015006666/tsla-10q_20150630.htm" xr:uid="{1D64F266-9A9E-482B-9EC8-E42E5B18CC98}"/>
+    <hyperlink ref="X1" r:id="rId87" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459015009741/tsla-10q_20150930.htm" xr:uid="{A7852F4C-FAD4-4639-B7AF-42FB5109597D}"/>
+    <hyperlink ref="Y1" r:id="rId88" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459016013195/tsla-10k_20151231.htm" xr:uid="{B3E9B1E8-FFB5-47F6-AF8C-8E4D3E3DDB82}"/>
+    <hyperlink ref="Z1" r:id="rId89" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459016018886/tsla-10q_20160331.htm" xr:uid="{0FE92F43-6935-4AD6-AD63-4FE06F79328B}"/>
+    <hyperlink ref="AA1" r:id="rId90" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459016023024/tsla-10q_20160630.htm" xr:uid="{190A3802-D205-4A25-8F78-74455961E466}"/>
+    <hyperlink ref="AB1" r:id="rId91" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459016026820/tsla-10q_20160930.htm" xr:uid="{4183B870-FF12-4F84-8B63-059FDD21C270}"/>
+    <hyperlink ref="AC1" r:id="rId92" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459017003118/tsla-10k_20161231.htm" xr:uid="{BDB5A99A-FF38-4445-8EF1-9DAE81B56490}"/>
+    <hyperlink ref="AD1" r:id="rId93" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459017009968/tsla-10q_20170331.htm" xr:uid="{D716AB80-D634-4F08-9667-63B7BF70AD66}"/>
+    <hyperlink ref="AE1" r:id="rId94" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459017015705/tsla-10q_20170630.htm" xr:uid="{9054AE92-A438-4359-BC0C-EFD62A80EF7B}"/>
+    <hyperlink ref="AF1" r:id="rId95" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459017021343/tsla-10q_20170930.htm" xr:uid="{B1466D89-217F-4F03-9075-3AEF777FBA75}"/>
+    <hyperlink ref="AG1" r:id="rId96" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459018002956/tsla-10k_20171231.htm" xr:uid="{C4BF15A3-395C-4652-8B98-D3FC5801414C}"/>
+    <hyperlink ref="AH1" r:id="rId97" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459018011086/tsla-10q_20180331.htm" xr:uid="{6BFE511E-3698-4E51-8A2E-56EB0E4E375D}"/>
+    <hyperlink ref="AI1" r:id="rId98" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459018019254/tsla-10q_20180630.htm" xr:uid="{DBC74BF5-D245-4BB9-BBF3-E5EBCC2ADF5B}"/>
+    <hyperlink ref="AJ1" r:id="rId99" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459018026353/tsla-10q_20180930.htm" xr:uid="{B530955D-5B2D-4B0C-834C-549CFBEE57D0}"/>
+    <hyperlink ref="AK1" r:id="rId100" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459019003165/tsla-10k_20181231.htm" xr:uid="{C8F953FF-914F-43E0-9424-35156E92846E}"/>
+    <hyperlink ref="AL1" r:id="rId101" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459019013462/tsla-10q_20190331.htm" xr:uid="{5C90B9C3-8E80-4278-9787-6541BF459848}"/>
+    <hyperlink ref="AM1" r:id="rId102" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459019026445/tsla-10q_20190630.htm" xr:uid="{485A2BF2-9CFE-4D32-88D7-5AAF6D0AA795}"/>
+    <hyperlink ref="AN1" r:id="rId103" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459019038256/tsla-10q_20190930.htm" xr:uid="{773F6C9D-1FF3-4359-91CF-6954BF880826}"/>
+    <hyperlink ref="AO1" r:id="rId104" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459020004475/tsla-10k_20191231.htm" xr:uid="{5D71E6DD-7166-4204-9EE7-10B65CAE1770}"/>
+    <hyperlink ref="AP1" r:id="rId105" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459020019931/tsla-10q_20200331.htm" xr:uid="{EEB0BFDA-65B1-4648-B6BB-064712E5CEA0}"/>
+    <hyperlink ref="AQ1" r:id="rId106" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459020033670/tsla-10q_20200630.htm" xr:uid="{972452CA-D308-45A8-9EDC-5DEA9E203A3E}"/>
+    <hyperlink ref="AR1" r:id="rId107" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459020047486/tsla-10q_20200930.htm" xr:uid="{3D59AD64-179E-4EEB-BA31-E6E036602F0D}"/>
+    <hyperlink ref="AS1" r:id="rId108" display="https://www.sec.gov/Archives/edgar/data/1318605/000156459021004599/tsla-10k_20201231.htm" xr:uid="{76B72A3D-536E-47AC-BBF9-E348E5B0C15C}"/>
+    <hyperlink ref="AT1" r:id="rId109" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017021000046/tsla-20210331.htm" xr:uid="{9752ABC4-872A-4355-9199-EEF2EEC216B3}"/>
+    <hyperlink ref="AU1" r:id="rId110" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017021000524/tsla-20210630.htm" xr:uid="{BD4EDA26-90F9-4BED-9BCC-5672468A61BC}"/>
+    <hyperlink ref="AV1" r:id="rId111" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017021002253/tsla-20210930.htm" xr:uid="{13226733-FC56-43F5-9F96-DBF6351D68EA}"/>
+    <hyperlink ref="AW1" r:id="rId112" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017022000796/tsla-20211231.htm" xr:uid="{3961BCF4-5857-4B98-B75D-EC1A397CB7EC}"/>
+    <hyperlink ref="AX1" r:id="rId113" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017022006034/tsla-20220331.htm" xr:uid="{2603005F-03FE-481C-A048-D4EB34A387E4}"/>
+    <hyperlink ref="AY1" r:id="rId114" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017022012936/tsla-20220630.htm" xr:uid="{7AF28E03-5B02-4858-B4F4-3261F612858A}"/>
+    <hyperlink ref="AZ1" r:id="rId115" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017022019867/tsla-20220930.htm" xr:uid="{38CD72A6-520E-4C07-8D04-E970D827B1BC}"/>
+    <hyperlink ref="BA1" r:id="rId116" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017023001409/tsla-20221231.htm" xr:uid="{E5FF5610-5BE1-4BB6-8713-F0002D84F9D0}"/>
+    <hyperlink ref="BB1" r:id="rId117" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017023013890/tsla-20230331.htm" xr:uid="{C4E173EB-5F50-4D60-999E-9414603DAE90}"/>
+    <hyperlink ref="BC1" r:id="rId118" display="https://www.sec.gov/Archives/edgar/data/1318605/000095017023033872/tsla-20230630.htm" xr:uid="{735C82F7-7763-4AA1-ABA5-6673443F85CF}"/>
+    <hyperlink ref="BD1" r:id="rId119" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828023034847/tsla-20230930.htm" xr:uid="{D4389C95-DCCD-4B66-BBCD-E98548744B98}"/>
+    <hyperlink ref="BE1" r:id="rId120" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828024002390/tsla-20231231.htm" xr:uid="{1EDA8EB8-6918-47FA-BE09-987E389CB5D5}"/>
+    <hyperlink ref="BF1" r:id="rId121" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828024017503/tsla-20240331.htm" xr:uid="{F72A76A1-5C5E-40E2-817D-FEEF38C6CFEE}"/>
+    <hyperlink ref="BG1" r:id="rId122" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828024032662/tsla-20240630.htm" xr:uid="{B462D06F-DDF8-4419-ABB8-CD682378B597}"/>
+    <hyperlink ref="BH1" r:id="rId123" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828024043486/tsla-20240930.htm" xr:uid="{B945E329-E1D4-467E-A741-27F02AF4B1C9}"/>
+    <hyperlink ref="BI1" r:id="rId124" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828025003063/tsla-20241231.htm" xr:uid="{DA8B97B2-26BB-4C34-A762-7A905960B904}"/>
+    <hyperlink ref="BJ1" r:id="rId125" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828025018911/tsla-20250331.htm" xr:uid="{132CA946-F361-4006-8B28-A16FCD5EEBB1}"/>
+    <hyperlink ref="BK1" r:id="rId126" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828025035806/tsla-20250630.htm" xr:uid="{53B339CE-9B8A-4C39-8559-0C1469C5A875}"/>
+    <hyperlink ref="BL1" r:id="rId127" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828025045968/tsla-20250930.htm" xr:uid="{6381C7A2-F6FE-457D-B5A3-BBF9BA50F1A9}"/>
+    <hyperlink ref="BM1" r:id="rId128" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828026003952/tsla-20251231.htm" xr:uid="{516B7952-A424-4AB3-A60C-6EA10321825A}"/>
+    <hyperlink ref="BN1" r:id="rId129" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828026026673/tsla-20260331.htm" xr:uid="{C3090D6F-B7CA-42A3-AE7B-676407925FD0}"/>
+    <hyperlink ref="BO1" r:id="rId130" display="https://www.sec.gov/Archives/edgar/data/1318605/000162828026049270/tsla-20260630.htm" xr:uid="{32CF75E3-719C-4021-912C-7090285E0549}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId66"/>
-  <legacyDrawing r:id="rId67"/>
+  <drawing r:id="rId131"/>
+  <legacyDrawing r:id="rId132"/>
 </worksheet>
 </file>